--- a/results/job_matches_2026-06-25.xlsx
+++ b/results/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,117 +783,117 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Insurance Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CCMSI</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Danville, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db60959b33c4c354</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f17df007528af5</t>
+          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67ad259f5f7452d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python Technical Specialist - Data Analysis, SQL</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,38 +902,38 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7208f4d9e700b7c7</t>
+          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,94 +941,94 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
+          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
+          <t>https://www.indeed.com/viewjob?jk=97eae083068a3900</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
+          <t>https://www.indeed.com/viewjob?jk=7fcb837d7fc08d9c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,73 +1042,73 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
+          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
+          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
+          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
+          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Full Stack Data Science Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,369 +1196,369 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
+          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
+          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Covington, KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
+          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
+          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
+          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>iEnjoy Home</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>National Grid</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
+          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Azure Senior Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala, DataOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Pedigree Technologies LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9914638c19a8a4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,1223 +1567,1223 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
+          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
+          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>SDE I- Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
+          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
+          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EWC Corporate LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
+          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
+          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Data Engineer II/III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nimble Robotics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Data Workflow Engineer – AI &amp; Automation Focus</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
+          <t>https://www.indeed.com/viewjob?jk=461aa75a8d591411</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
+          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Sr. Software Development Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Sr Solutions Architect - Omnichannel</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
+          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
+          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
+          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Jonas Software</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>14.6</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef996c4dca600f0c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
+          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>AI Identity Security Engineer (SailPoint)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
+          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Software Engineer - Limited Tenure - Hybrid</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Sr. Production Support Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
+          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97eae083068a3900</t>
+          <t>https://www.indeed.com/viewjob?jk=fe70c0ae09b9a043</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>GCP Senior Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2792,46 +2792,46 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
+          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
+          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>ForgeRock Federation Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
+          <t>https://www.indeed.com/viewjob?jk=1df9b945be5959e8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Architect – Capital Markets Domain</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MEDIIT</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,172 +2911,172 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df069435d852166</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Senior Demo Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
+          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>DataOS Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Cloud Platform Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
+          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full Stack Data Science Engineer</t>
+          <t>DevOps Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>AGFA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
+          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Senior Data Architect</t>
+          <t>Sr. Business Applications Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>LeMaitre Vascular</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala, DataOps</t>
+          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Dexter Systems Inc</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Covington, KY, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Business Intelligence Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
+          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>iEnjoy Home</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
+          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>Mad Mobile</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, S3, ECS, RDS, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
+          <t>https://www.indeed.com/viewjob?jk=912fd59f7f797fb3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Python Developer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, Lambda, ECS, Scala, PostgreSQL, Docker, Kubernetes, pytest, Python, SQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ca06fa6ac3ac22</t>
+          <t>https://www.indeed.com/viewjob?jk=21327b99c0a351e9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SDE I- Adobe Exp Platform</t>
+          <t>Product Engineer II - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Azure, Oracle, SQL Server, PostgreSQL, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3365,1686 +3365,6 @@
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>DataArt</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Expleo Group</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>EWC Corporate LLC</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Dearborn, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Machine learning Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Pennington, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Vforce Infotech</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Edison, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Sr. Software Development Engineer, Platform Engineering</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>PitchBook</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Wellington Management</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Data Workflow Engineer – AI &amp; Automation Focus</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Digital Realty</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=461aa75a8d591411</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>ClearCaptions, LLC</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Engineering Supervisor</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Waco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Engineering Supervisor</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Waco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Sr Solutions Architect - Omnichannel</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Space Communications)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Space Communications)</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>OneMain Financial</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0edcab6ac0afe9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Software Engineer - Intern</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Jonas Software</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef996c4dca600f0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>AI Identity Security Engineer (SailPoint)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Regions Financial</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Hoover, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Software Engineer - Limited Tenure - Hybrid</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Mayo Clinic</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Rochester, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Databricks Devops</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6dec79ae33f75455</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Arrive Logistics</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Central Garden &amp; Pet</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Schaumburg, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Central Garden &amp; Pet</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Walnut Creek, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Database Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Chess.com</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe70c0ae09b9a043</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>GCP Senior Data Architect</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>MDM/DG SME/Architect</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>PI Technologies LLC</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, ELT, Talend, Tableau</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=869da5c5f350a735</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Platform Database Engineer (MONGO DB)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Valtech Group</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, MongoDB, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2103580026ffe43a</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Data Migration Architect</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Oracle, SQL Server</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6708bcfc3951fe3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>ForgeRock Federation Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Peraton</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Chantilly, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1df9b945be5959e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>DataOS Data Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Vancouver, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Demo Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Keeper Security, Inc.</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Cloud Platform Engineer II</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>University of Utah</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Engineer 2</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>EMCOR</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Tonawanda, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>DevOps Developer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>AGFA</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>HCLTech</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Data Warehouse Developer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Dexter Systems Inc</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Analytics and AI Developer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Rochester Electronics</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Newburyport, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Business Intelligence Engineer II</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Sr Data Architect</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>TruStage</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer, Digital Engineering</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Vuori</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Carlsbad, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Python Developer II</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Finance of America</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, Scala, PostgreSQL, Docker, Kubernetes, pytest, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21327b99c0a351e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Product Engineer II - Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Esri</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Redlands, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, RDS, Azure, Oracle, SQL Server, PostgreSQL, AWS CloudFormation, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4172ffc795a8a9ef</t>
         </is>

--- a/results/job_matches_2026-06-25.xlsx
+++ b/results/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,35 +538,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Python or GoLang Software Engineer - 2 days onsite (Chicago, IL) - FreeWheel</t>
+          <t>Senior Data Engineer on-site)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e805afd8491439b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91ab31afe36f91</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91ab31afe36f91</t>
+          <t>https://www.indeed.com/viewjob?jk=13b180e2e10be4d8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer on-site)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b180e2e10be4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=90aa58aa706914e5</t>
         </is>
       </c>
     </row>
@@ -783,35 +783,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Architect, Technology I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
+          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
+          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97eae083068a3900</t>
+          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcb837d7fc08d9c</t>
+          <t>https://www.indeed.com/viewjob?jk=97eae083068a3900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
+          <t>https://www.indeed.com/viewjob?jk=9143d5f91657ba93</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
+          <t>https://www.indeed.com/viewjob?jk=7fcb837d7fc08d9c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,64 +1116,64 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
+          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Data Science Engineer</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
+          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Azure Senior Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala, DataOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Covington, KY, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
+          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Covington, KY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
+          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>iEnjoy Home</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
+          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>iEnjoy Home</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
+          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azure Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>National Grid</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala, DataOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
+          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
+          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
+          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
+          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
+          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SDE I- Adobe Exp Platform</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
+          <t>SDE I- Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
+          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EWC Corporate LLC</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
+          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>EWC Corporate LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II/III</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nimble Robotics</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
+          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Workflow Engineer – AI &amp; Automation Focus</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461aa75a8d591411</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Development Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer, Platform Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II/III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Nimble Robotics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
+          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Workflow Engineer – AI &amp; Automation Focus</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=461aa75a8d591411</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
+          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
+          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
+          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Omnichannel</t>
+          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Space Communications)</t>
+          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Space Communications)</t>
+          <t>Sr Solutions Architect - Omnichannel</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
+          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer - Intern</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jonas Software</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef996c4dca600f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
+          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Jonas Software</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
+          <t>https://www.indeed.com/viewjob?jk=ef996c4dca600f0c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Identity Security Engineer (SailPoint)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
+          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Limited Tenure - Hybrid</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
+          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Identity Security Engineer (SailPoint)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
+          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer - Limited Tenure - Hybrid</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
+          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Production Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe70c0ae09b9a043</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GCP Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
+          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Production Support Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
+          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ForgeRock Federation Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df9b945be5959e8</t>
+          <t>https://www.indeed.com/viewjob?jk=fe70c0ae09b9a043</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6dc9ebd6a9ade1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Demo Platform Engineer</t>
+          <t>GCP Senior Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
+          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DataOS Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer II</t>
+          <t>ForgeRock Federation Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
+          <t>https://www.indeed.com/viewjob?jk=1df9b945be5959e8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps Developer</t>
+          <t>DataOS Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AGFA</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Business Applications Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LeMaitre Vascular</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Demo Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dexter Systems Inc</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
+          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Analytics and AI Developer</t>
+          <t>Cloud Platform Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
+          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II</t>
+          <t>Senior Software Engineer, Back-End (Payments)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Collectors</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,19 +3191,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>DevOps Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>AGFA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
+          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Sr. Business Applications Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>LeMaitre Vascular</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mad Mobile</t>
+          <t>Dexter Systems Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, Kafka, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912fd59f7f797fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Python Developer II</t>
+          <t>Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Finance of America</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Scala, PostgreSQL, Docker, Kubernetes, pytest, Python, SQL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21327b99c0a351e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Product Engineer II - Cloud Infrastructure</t>
+          <t>Business Intelligence Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Oracle, SQL Server, PostgreSQL, AWS CloudFormation, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,77 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172ffc795a8a9ef</t>
+          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Aivra Health</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Python Developer II</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Finance of America</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, PostgreSQL, Docker, Kubernetes, pytest, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21327b99c0a351e9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-25.xlsx
+++ b/results/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Data - Archimedes</t>
+          <t>Senior Data Engineer on-site)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.6</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00efdae7133cac10</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91ab31afe36f91</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Senior Data Engineer on-site)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.9</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ac01a3b37b1411</t>
+          <t>https://www.indeed.com/viewjob?jk=13b180e2e10be4d8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer on-site)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91ab31afe36f91</t>
+          <t>https://www.indeed.com/viewjob?jk=90aa58aa706914e5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer on-site)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>NinjaTrader</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, GCP, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b180e2e10be4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bde68b2f181a8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,137 +636,137 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90aa58aa706914e5</t>
+          <t>https://www.indeed.com/viewjob?jk=9de4453bf3c4212f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Data Engineer-Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea98351890cb41a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2fc4d359a22654</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Architect, Technology I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NinjaTrader</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, GCP, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bde68b2f181a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Development Operations - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849fb6429e007fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer-Adobe Exp Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2fc4d359a22654</t>
+          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Architect, Technology I</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
+          <t>https://www.indeed.com/viewjob?jk=97eae083068a3900</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Intelligence Sr Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e1d0952eadd1803</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,172 +881,172 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
+          <t>https://www.indeed.com/viewjob?jk=9143d5f91657ba93</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
+          <t>https://www.indeed.com/viewjob?jk=7fcb837d7fc08d9c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
+          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Sr. Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
+          <t>https://www.indeed.com/viewjob?jk=e360f490049f028c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Azure Senior Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala, DataOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97eae083068a3900</t>
+          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9143d5f91657ba93</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcb837d7fc08d9c</t>
+          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Covington, KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
+          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,94 +1161,94 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
+          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
+          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>iEnjoy Home</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>National Grid</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala, DataOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
+          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Covington, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
+          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>iEnjoy Home</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
+          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pedigree Technologies LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, MySQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9914638c19a8a4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Pedigree Technologies LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9914638c19a8a4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>SDE I- Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
+          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>EWC Corporate LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
+          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
+          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SDE I- Adobe Exp Platform</t>
+          <t>Sr. Software Development Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II/III</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EWC Corporate LLC</t>
+          <t>Nimble Robotics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
+          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Data Workflow Engineer – AI &amp; Automation Focus</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=461aa75a8d591411</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
+          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer, Platform Engineering</t>
+          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Solutions Architect - Omnichannel</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
+          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer II/III</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nimble Robotics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
+          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Workflow Engineer – AI &amp; Automation Focus</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461aa75a8d591411</t>
+          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
+          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AI Identity Security Engineer (SailPoint)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
+          <t>Software Engineer - Limited Tenure - Hybrid</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
+          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
+          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Omnichannel</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Space Communications)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Space Communications)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,94 +2491,94 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer - Intern</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jonas Software</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef996c4dca600f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6dc9ebd6a9ade1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Identity Security Engineer (SailPoint)</t>
+          <t>Sr. Production Support Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
+          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer - Limited Tenure - Hybrid</t>
+          <t>GCP Senior Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
+          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
+          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>ForgeRock Federation Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
+          <t>https://www.indeed.com/viewjob?jk=1df9b945be5959e8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DataOS Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Demo Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
+          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Production Support Engineer</t>
+          <t>Cloud Platform Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
+          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Software Engineer, Back-End (Payments)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Collectors</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe70c0ae09b9a043</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6dc9ebd6a9ade1</t>
+          <t>https://www.indeed.com/viewjob?jk=7b74098577c0fc14</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GCP Senior Data Architect</t>
+          <t>DevOps Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>AGFA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
+          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Business Applications Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>LeMaitre Vascular</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ForgeRock Federation Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Dexter Systems Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df9b945be5959e8</t>
+          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DataOS Data Engineer</t>
+          <t>Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Business Intelligence Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Demo Platform Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
+          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer II</t>
+          <t>Python Developer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Finance of America</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, ECS, Scala, PostgreSQL, Docker, Kubernetes, pytest, Python, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3155,286 +3155,6 @@
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Back-End (Payments)</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Collectors</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>DevOps Developer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>AGFA</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Sr. Business Applications Developer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>LeMaitre Vascular</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Burlington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Data Warehouse Developer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Dexter Systems Inc</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Analytics and AI Developer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Rochester Electronics</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Newburyport, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Business Intelligence Engineer II</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Python Developer II</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Finance of America</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, Scala, PostgreSQL, Docker, Kubernetes, pytest, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=21327b99c0a351e9</t>
         </is>

--- a/results/job_matches_2026-06-25.xlsx
+++ b/results/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
+          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
+          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Omnichannel</t>
+          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Space Communications)</t>
+          <t>Sr Solutions Architect - Omnichannel</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,69 +2271,69 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
+          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Identity Security Engineer (SailPoint)</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
+          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - Limited Tenure - Hybrid</t>
+          <t>AI Identity Security Engineer (SailPoint)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
+          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Limited Tenure - Hybrid</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
+          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
+          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6dc9ebd6a9ade1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr. Production Support Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6dc9ebd6a9ade1</t>
+          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Production Support Engineer</t>
+          <t>GCP Senior Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
+          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GCP Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
+          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ForgeRock Federation Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
+          <t>https://www.indeed.com/viewjob?jk=1df9b945be5959e8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ForgeRock Federation Engineer</t>
+          <t>DataOS Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df9b945be5959e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DataOS Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Demo Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Demo Platform Engineer</t>
+          <t>Cloud Platform Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer II</t>
+          <t>Senior Software Engineer, Back-End (Payments)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Collectors</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Payments)</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Collectors</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
+          <t>https://www.indeed.com/viewjob?jk=7b74098577c0fc14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>DevOps Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AGFA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b74098577c0fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DevOps Developer</t>
+          <t>Sr. Business Applications Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AGFA</t>
+          <t>LeMaitre Vascular</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Business Applications Developer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LeMaitre Vascular</t>
+          <t>Dexter Systems Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
+          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dexter Systems Inc</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics and AI Developer</t>
+          <t>Business Intelligence Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
+          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,77 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Python Developer II</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Finance of America</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, Scala, PostgreSQL, Docker, Kubernetes, pytest, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21327b99c0a351e9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-25.xlsx
+++ b/results/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Architect, Technology I</t>
+          <t>Artificial Intelligence/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
+          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Architect, Technology I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,59 +776,59 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97eae083068a3900</t>
+          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Business Intelligence Sr Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e1d0952eadd1803</t>
+          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Business Intelligence Sr Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9143d5f91657ba93</t>
+          <t>https://www.indeed.com/viewjob?jk=0e1d0952eadd1803</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcb837d7fc08d9c</t>
+          <t>https://www.indeed.com/viewjob?jk=9143d5f91657ba93</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
+          <t>https://www.indeed.com/viewjob?jk=7fcb837d7fc08d9c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, Data - FreeWheel</t>
+          <t>DevOps Engineer with Java</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e360f490049f028c</t>
+          <t>https://www.indeed.com/viewjob?jk=91621af2058bcdaf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Senior Data Architect</t>
+          <t>DevOps Engineer with Java</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
+          <t>https://www.indeed.com/viewjob?jk=e4043bb7b561d2d9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>Sr. Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=e360f490049f028c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Covington, KY, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Covington, KY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
+          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>iEnjoy Home</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
+          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
+          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>iEnjoy Home</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
+          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
+          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Software Engineer - Application Consultant</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=649b76151ccd01db</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Software Engineer - Application Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e983e1a21daa953c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Pedigree Technologies LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9914638c19a8a4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
+          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
+          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pedigree Technologies LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, MySQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9914638c19a8a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SDE I- Adobe Exp Platform</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
+          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
+          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EWC Corporate LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>SDE I- Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EWC Corporate LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1812,46 +1812,46 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, Lambda, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer, Platform Engineering</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
+          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Workflow Engineer – AI &amp; Automation Focus</t>
+          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=461aa75a8d591411</t>
+          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Software Development Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
+          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
+          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Omnichannel</t>
+          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Space Communications)</t>
+          <t>Sr Solutions Architect - Omnichannel</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,69 +2306,69 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
+          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Identity Security Engineer (SailPoint)</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
+          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Limited Tenure - Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
+          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
+          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Identity Security Engineer (SailPoint)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
+          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer - Limited Tenure - Hybrid</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6dc9ebd6a9ade1</t>
+          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Production Support Engineer</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
+          <t>https://www.indeed.com/viewjob?jk=4716c280fcc00d98</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP Senior Data Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6dc9ebd6a9ade1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Production Support Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
+          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ForgeRock Federation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,94 +2666,94 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df9b945be5959e8</t>
+          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DataOS Data Engineer</t>
+          <t>Alteryx Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>MESTEK INC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=1b49305ad894f414</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Demo Platform Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Payments)</t>
+          <t>Senior Demo Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Collectors</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
+          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>DataOS Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b74098577c0fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps Developer</t>
+          <t>Cloud Platform Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AGFA</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Business Applications Developer</t>
+          <t>Senior Application Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LeMaitre Vascular</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dexter Systems Inc</t>
+          <t>Coralogix</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, GCP, Scala, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
+          <t>https://www.indeed.com/viewjob?jk=35aecec750568de1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Analytics and AI Developer</t>
+          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II</t>
+          <t>Senior Software Engineer, Back-End (Payments)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Collectors</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,192 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b74098577c0fc14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DevOps Developer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AGFA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sr. Business Applications Developer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LeMaitre Vascular</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Burlington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Warehouse Developer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Dexter Systems Inc</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Analytics and AI Developer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Rochester Electronics</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Newburyport, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer II</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-25.xlsx
+++ b/results/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer on-site)</t>
+          <t>Databricks Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91ab31afe36f91</t>
+          <t>https://www.indeed.com/viewjob?jk=d57ef47d055269a5</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b180e2e10be4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91ab31afe36f91</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer on-site)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90aa58aa706914e5</t>
+          <t>https://www.indeed.com/viewjob?jk=13b180e2e10be4d8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NinjaTrader</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, GCP, BigQuery, Cloud Storage</t>
+          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bde68b2f181a8</t>
+          <t>https://www.indeed.com/viewjob?jk=90aa58aa706914e5</t>
         </is>
       </c>
     </row>
@@ -643,52 +643,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer-Adobe Exp Platform</t>
+          <t>Artificial Intelligence/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2fc4d359a22654</t>
+          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Engineer</t>
+          <t>Senior Architect, Technology I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Architect, Technology I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Dematic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Spanner Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
+          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
+          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Software Engineer - 2373458</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Software Engineer - Application Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
+          <t>https://www.indeed.com/viewjob?jk=649b76151ccd01db</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Application Consultant</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>iEnjoy Home</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
+          <t>https://www.indeed.com/viewjob?jk=e983e1a21daa953c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Pedigree Technologies LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9914638c19a8a4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer - Application Consultant</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649b76151ccd01db</t>
+          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - Application Consultant</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e983e1a21daa953c</t>
+          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pedigree Technologies LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, MySQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9914638c19a8a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
+          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
+          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
+          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,77 +1676,77 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Kafka, Splunk, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
+          <t>https://www.indeed.com/viewjob?jk=b16300c5f378062d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed62df8d733ccc6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SDE I- Adobe Exp Platform</t>
+          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
+          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
+          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Sr Software Engineer, Data Science</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e77b1dd58e37d2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II/III</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nimble Robotics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
+          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Hadoop, Hive, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Maven</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
+          <t>https://www.indeed.com/viewjob?jk=76da2dc311d12db7</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
+          <t>https://www.indeed.com/viewjob?jk=58e6cb2128aca867</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer, Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer II/III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Nimble Robotics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
+          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
+          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
+          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Omnichannel</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Sonny's Enterprises, Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Space Communications)</t>
+          <t>IS Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Menards</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8cc0d2a437f129</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Space Communications)</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
+          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,207 +2421,207 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
+          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
+          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Identity Security Engineer (SailPoint)</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
+          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer - Limited Tenure - Hybrid</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Sr Solutions Architect - Omnichannel</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4716c280fcc00d98</t>
+          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6dc9ebd6a9ade1</t>
+          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Production Support Engineer</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
+          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alteryx Developer</t>
+          <t>AI Identity Security Engineer (SailPoint)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MESTEK INC</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b49305ad894f414</t>
+          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Software Engineer - Limited Tenure - Hybrid</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,77 +2726,77 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
+          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
+          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Demo Platform Engineer</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4716c280fcc00d98</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DataOS Data Engineer</t>
+          <t>Sr. Production Support Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer II</t>
+          <t>Ontology Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
+          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Application Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
+          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Coralogix</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, GCP, Scala, Splunk, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35aecec750568de1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
+          <t>DataOS Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Payments)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Collectors</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
+          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,29 +3076,29 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b74098577c0fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DevOps Developer</t>
+          <t>Senior Demo Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AGFA</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Business Applications Developer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LeMaitre Vascular</t>
+          <t>Coralogix</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, GCP, Scala, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
+          <t>https://www.indeed.com/viewjob?jk=35aecec750568de1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Application Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dexter Systems Inc</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analytics and AI Developer</t>
+          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,192 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b74098577c0fc14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Back-End (Payments)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Collectors</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sr. Business Applications Developer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LeMaitre Vascular</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Burlington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Business Intelligence Engineer II</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Full Stack AI Developer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Invovia</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DevOps Developer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AGFA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-25.xlsx
+++ b/results/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,42 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57ef47d055269a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c61bc90da42df2de</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer on-site)</t>
+          <t>Databricks Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91ab31afe36f91</t>
+          <t>https://www.indeed.com/viewjob?jk=d57ef47d055269a5</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b180e2e10be4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91ab31afe36f91</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer on-site)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ziosk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, RDS, Azure, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90aa58aa706914e5</t>
+          <t>https://www.indeed.com/viewjob?jk=13b180e2e10be4d8</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Engineer</t>
+          <t>Senior Software Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
+          <t>https://www.indeed.com/viewjob?jk=a32a20237152630a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Architect, Technology I</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Atlas Group LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
+          <t>https://www.indeed.com/viewjob?jk=96986685e9f66259</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dematic</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCP Spanner Data Engineer</t>
+          <t>Senior Architect, Technology I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Dematic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,129 +811,129 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>GCP Spanner Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
+          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Intelligence Sr Analyst</t>
+          <t>Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e1d0952eadd1803</t>
+          <t>https://www.indeed.com/viewjob?jk=d94580e77e2d3def</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9143d5f91657ba93</t>
+          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fcb837d7fc08d9c</t>
+          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer with Java</t>
+          <t>Business Intelligence Sr Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91621af2058bcdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=0e1d0952eadd1803</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer with Java</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4043bb7b561d2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9143d5f91657ba93</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, MySQL, MongoDB, DynamoDB, Azure Cosmos DB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,164 +1056,164 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
+          <t>https://www.indeed.com/viewjob?jk=7fcb837d7fc08d9c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, Data - FreeWheel</t>
+          <t>Senior Data Engineer, AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e360f490049f028c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>DevOps Engineer with Java</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=91621af2058bcdaf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>DevOps Engineer with Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=e4043bb7b561d2d9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Covington, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
+          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2373458</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mourant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
+          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer - Application Consultant</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649b76151ccd01db</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - Application Consultant</t>
+          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e983e1a21daa953c</t>
+          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pedigree Technologies LLC</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Covington, KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9914638c19a8a4</t>
+          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Senior Software Engineer - 2373458</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
+          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Software Engineer - Application Consultant</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
+          <t>https://www.indeed.com/viewjob?jk=649b76151ccd01db</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Software Engineer - Application Consultant</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=e983e1a21daa953c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Pedigree Technologies LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9914638c19a8a4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
+          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>IT Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Nexzentek</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
+          <t>https://www.indeed.com/viewjob?jk=b58e4f761ccad015</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,77 +1676,77 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Splunk, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b16300c5f378062d</t>
+          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed62df8d733ccc6</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
+          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EWC Corporate LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Data Science</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, Splunk, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e77b1dd58e37d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b16300c5f378062d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed62df8d733ccc6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>DataArt</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
+          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
+          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Python, AWS Glue, Airflow, Lambda)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Hadoop, Hive, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, Maven</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76da2dc311d12db7</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b49a1ca173ef5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer, Data Science</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e6cb2128aca867</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e77b1dd58e37d2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Finance</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
+          <t>https://www.indeed.com/viewjob?jk=a49c234a0c6d1d83</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II/III</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nimble Robotics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
+          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
+          <t>https://www.indeed.com/viewjob?jk=58e6cb2128aca867</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sonny's Enterprises, Inc</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f6e8fec3f48d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IS Quality Assurance Engineer</t>
+          <t>Data Engineer II/III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Menards</t>
+          <t>Nimble Robotics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8cc0d2a437f129</t>
+          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
+          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
+          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
+          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
+          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
+          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>IS Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Menards</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8cc0d2a437f129</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Omnichannel</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Sonny's Enterprises, Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Space Communications)</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Space Communications)</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Identity Security Engineer (SailPoint)</t>
+          <t>Sr Solutions Architect - Omnichannel</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer - Limited Tenure - Hybrid</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
+          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
+          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
+          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Sr. Production Support Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4716c280fcc00d98</t>
+          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Production Support Engineer</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ELEVI Associates, LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
+          <t>https://www.indeed.com/viewjob?jk=bef5e0cbd24f1e8d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ontology Engineer</t>
+          <t>Senior Software Engineer (PHP)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, SQS, ECS, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
+          <t>https://www.indeed.com/viewjob?jk=4716c280fcc00d98</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Ontology Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
+          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
         </is>
       </c>
     </row>
@@ -2988,25 +2988,25 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DataOS Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
         </is>
       </c>
     </row>
@@ -3128,12 +3128,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Technical Support Engineer</t>
+          <t>Senior Software Engineer, Back-End (Payments)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Coralogix</t>
+          <t>Collectors</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, GCP, Scala, Splunk, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35aecec750568de1</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Application Engineer</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Coralogix</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, GCP, Scala, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
+          <t>https://www.indeed.com/viewjob?jk=35aecec750568de1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
+          <t>Senior Application Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Full Stack AI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b74098577c0fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Payments)</t>
+          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Collectors</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Business Applications Developer</t>
+          <t>DevOps Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LeMaitre Vascular</t>
+          <t>AGFA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
+          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II</t>
+          <t>Sr. Business Applications Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>LeMaitre Vascular</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,77 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Full Stack AI Developer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Invovia</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>DevOps Developer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>AGFA</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-25.xlsx
+++ b/results/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer on-site)</t>
+          <t>Sr. Site Reliability Engineer, Data - FreeWheel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91ab31afe36f91</t>
+          <t>https://www.indeed.com/viewjob?jk=9de4453bf3c4212f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer on-site)</t>
+          <t>Senior Software Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b180e2e10be4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a32a20237152630a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer, Data - FreeWheel</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Atlas Group LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de4453bf3c4212f</t>
+          <t>https://www.indeed.com/viewjob?jk=96986685e9f66259</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Data Engineer (Contract)</t>
+          <t>Artificial Intelligence/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a32a20237152630a</t>
+          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Architect, Technology I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Atlas Group LLC</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96986685e9f66259</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Dematic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Architect, Technology I</t>
+          <t>GCP Spanner Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
+          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PLM Teamcenter Solution Architect - Siemens</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dematic</t>
+          <t>TAN45 TECH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9bde3d8a51e4f79</t>
+          <t>https://www.indeed.com/viewjob?jk=747fddb8b55540ea</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Spanner Data Engineer</t>
+          <t>Sr Developer, IT Applications</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Kafka, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d94580e77e2d3def</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr Developer, IT Applications</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94580e77e2d3def</t>
+          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=650467e40b62799c</t>
+          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Solutions Engineer - Hybrid/Durham,NC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Hadoop, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f85d13cad9b24073</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI</t>
+          <t>GCP Technical Specialist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
+          <t>https://www.indeed.com/viewjob?jk=a829451037364106</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer with Java</t>
+          <t>Senior Data Engineer, AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91621af2058bcdaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4043bb7b561d2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=91621af2058bcdaf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
+          <t>DevOps Engineer with Java</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
+          <t>https://www.indeed.com/viewjob?jk=e4043bb7b561d2d9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Solutions – Dallas – Associate, Software Engineering – 4208762</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mourant</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Spark, Scala, Kafka, Snowflake, Oracle, Cassandra, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
+          <t>https://www.indeed.com/viewjob?jk=440eb7ec7c9d835a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
+          <t>https://www.indeed.com/viewjob?jk=fd415a132048d89a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Mourant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008b7c533fc81ed0</t>
+          <t>https://www.indeed.com/viewjob?jk=bba01ebafe36cd2b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud / Kubernetes / Java)</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Covington, KY, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, Azure, GCP, Spark, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37ce86d12ab5f536</t>
+          <t>https://www.indeed.com/viewjob?jk=3bdaf4ef4ebe2d43</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2373458</t>
+          <t>Sr. AWS Data Architect (Remote)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
+          <t>https://www.indeed.com/viewjob?jk=436457a82fb3e61d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - Application Consultant</t>
+          <t>Senior Software Engineer - 2373458</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649b76151ccd01db</t>
+          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
         </is>
       </c>
     </row>
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e983e1a21daa953c</t>
+          <t>https://www.indeed.com/viewjob?jk=649b76151ccd01db</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer - Application Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pedigree Technologies LLC</t>
+          <t>Kyndryl</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fargo, ND, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, RDS, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, SQS, ECS, IAM, RDS, MySQL, DynamoDB, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9914638c19a8a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e983e1a21daa953c</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT Software Engineer</t>
+          <t>Senior Backend Developer/ DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexzentek</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b58e4f761ccad015</t>
+          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a810b0c25679667</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8dc06684d4c96d</t>
+          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a85653fa31d9ca</t>
+          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=709864093f47bded</t>
+          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2c3cd7f51666769</t>
+          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9facc91ff9daf6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e0cff1fdf275be1</t>
+          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Backend Developer/ DevSecOps Engineer</t>
+          <t>IT Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Nexzentek</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d6003e0cc9fff47</t>
+          <t>https://www.indeed.com/viewjob?jk=b58e4f761ccad015</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
+          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Data Engineer (Python, AWS Glue, Airflow, Lambda)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=d02b49a1ca173ef5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (Python, AWS Glue, Airflow, Lambda)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02b49a1ca173ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fdb23c6c263875</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Data Science</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,69 +2026,69 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e77b1dd58e37d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>Data Engineer, Finance</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a49c234a0c6d1d83</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer, Finance</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, ETL</t>
+          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49c234a0c6d1d83</t>
+          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
+          <t>https://www.indeed.com/viewjob?jk=58e6cb2128aca867</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e6cb2128aca867</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Crate and Barrel</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e58f6e8fec3f48d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II/III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Nimble Robotics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e58f6e8fec3f48d</t>
+          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer II/III</t>
+          <t>Associate - Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nimble Robotics</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b93268a5d9a09415</t>
+          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, IAM, RDS, Spark, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a364410377394ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Asset and Wealth Management)</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d7090362d091f78</t>
+          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Google Cloud Platform &amp; Infrastructure</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a3f2a51e0f48a69</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Sonny's Enterprises, Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IS Quality Assurance Engineer</t>
+          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Menards</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8cc0d2a437f129</t>
+          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
         </is>
       </c>
     </row>
@@ -2538,20 +2538,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sonny's Enterprises, Inc</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr. Production Support Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
+          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>ELEVI Associates, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Fort Meade, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
+          <t>https://www.indeed.com/viewjob?jk=bef5e0cbd24f1e8d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Ontology Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
+          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Omnichannel</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hydrafacial</t>
+          <t>Axon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426cdfa391f3efd4</t>
+          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Production Support Engineer</t>
+          <t>Sr. Software Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
+          <t>https://www.indeed.com/viewjob?jk=ef11c58ff0ce6339</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Senior Software Engineer, Back-End (Payments)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ELEVI Associates, LLC</t>
+          <t>Collectors</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Meade, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bef5e0cbd24f1e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Scala, MySQL, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4716c280fcc00d98</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ontology Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Terraform, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,94 +2946,94 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
+          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Sr. Business Applications Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>LeMaitre Vascular</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Terraform, Docker</t>
+          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
+          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Application Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, SQL Server, ETL, Power BI</t>
+          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78973ff1bb73f687</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Full Stack AI Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Blob Storage, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
+          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe81f601d9ad5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Demo Platform Engineer</t>
+          <t>Data Exchange Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Medical Mutual of Ohio</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dublin, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,29 +3111,29 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9119731d42f84</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back-End (Payments)</t>
+          <t>Technical Support Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Collectors</t>
+          <t>Coralogix</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3146,227 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Data Modeling, ELT, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, GCP, Scala, Splunk, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Technical Support Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Coralogix</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Azure, GCP, Scala, Splunk, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=35aecec750568de1</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Application Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>The Walt Disney Company</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Lake Buena Vista, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, ECS, Databricks, Snowflake, PostgreSQL, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Full Stack AI Developer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Invovia</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, NoSQL, pytest</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>DevOps Developer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>AGFA</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2924b464417a6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Sr. Business Applications Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>LeMaitre Vascular</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Burlington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Azure, Data Lake Storage, Spark, PySpark, Scala, SQL Server, ETL, ELT, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14f1f112ff2b5af</t>
         </is>
       </c>
     </row>
